--- a/Config/GameConfig/Datas/farmland/farmlandUnlock.xlsx
+++ b/Config/GameConfig/Datas/farmland/farmlandUnlock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\farmland\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286678AC-1121-40AD-A35C-42A3DF61CDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B869D56-29AE-44C2-A266-FB37F39605D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -914,90 +914,147 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>10006</v>
+      </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>10007</v>
+      </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>10008</v>
+      </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>10009</v>
+      </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>10010</v>
+      </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>10011</v>
+      </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>10012</v>
+      </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>10013</v>
+      </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>10014</v>
+      </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>10015</v>
+      </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>10016</v>
+      </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>10017</v>
+      </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>10018</v>
+      </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>10019</v>
+      </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>10020</v>
+      </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>10021</v>
+      </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>10022</v>
+      </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>10023</v>
+      </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>10024</v>
+      </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
     </row>

--- a/Config/GameConfig/Datas/farmland/farmlandUnlock.xlsx
+++ b/Config/GameConfig/Datas/farmland/farmlandUnlock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\farmland\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B869D56-29AE-44C2-A266-FB37F39605D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886AFC58-0644-439F-8BDD-11A2C4B4FE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -184,6 +184,69 @@
   <si>
     <t>list,item.ItemExchange</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000001,250</t>
+  </si>
+  <si>
+    <t>1000002,5</t>
+  </si>
+  <si>
+    <t>田地6</t>
+  </si>
+  <si>
+    <t>田地7</t>
+  </si>
+  <si>
+    <t>田地8</t>
+  </si>
+  <si>
+    <t>田地9</t>
+  </si>
+  <si>
+    <t>田地10</t>
+  </si>
+  <si>
+    <t>田地11</t>
+  </si>
+  <si>
+    <t>田地12</t>
+  </si>
+  <si>
+    <t>田地13</t>
+  </si>
+  <si>
+    <t>田地14</t>
+  </si>
+  <si>
+    <t>田地15</t>
+  </si>
+  <si>
+    <t>田地16</t>
+  </si>
+  <si>
+    <t>田地17</t>
+  </si>
+  <si>
+    <t>田地18</t>
+  </si>
+  <si>
+    <t>田地19</t>
+  </si>
+  <si>
+    <t>田地20</t>
+  </si>
+  <si>
+    <t>田地21</t>
+  </si>
+  <si>
+    <t>田地22</t>
+  </si>
+  <si>
+    <t>田地23</t>
+  </si>
+  <si>
+    <t>田地24</t>
   </si>
 </sst>
 </file>
@@ -917,144 +980,391 @@
       <c r="B11">
         <v>10006</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>10007</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="C12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>10008</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="C13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>10009</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="C14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14">
+        <v>9</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>10010</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="C15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>10011</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16">
+        <v>11</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>10012</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17">
+        <v>12</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>10013</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18">
+        <v>13</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>10014</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>10015</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>10016</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21">
+        <v>16</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>10017</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22">
+        <v>17</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>10018</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>10019</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24">
+        <v>19</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>10020</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25">
+        <v>20</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>10021</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26">
+        <v>21</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>10022</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27">
+        <v>22</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>10023</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28">
+        <v>23</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>10024</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29">
+        <v>24</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
     </row>
